--- a/ig/xdsdocuments/all-profiles.xlsx
+++ b/ig/xdsdocuments/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6004" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="674">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-homecareobservation-draft</t>
+    <t>0.1.0-homecareobservation-draft-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T11:19:10+00:00</t>
+    <t>2026-04-30T11:35:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,6 +644,18 @@
 </t>
   </si>
   <si>
+    <t>R5: An explicitly assigned identifer of a variation of the content in the DocumentReference (new)</t>
+  </si>
+  <si>
+    <t>R5: `DocumentReference.version` (new:string)</t>
+  </si>
+  <si>
+    <t>Element `DocumentReference.version` has a context of DocumentReference based on following the parent source element upwards and mapping to `DocumentReference`.
+Element `DocumentReference.version` has a context of Media based on following the parent source element upwards and mapping to `Media`.
+Element `DocumentReference.version` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+While each resource, including the DocumentReference itself, has its own version identifier, this is a formal identifier for the logical version of the DocumentReference as a whole. It would remain constant if the resources were moved to a new server, and all got new individual resource versions, for example.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -687,10 +699,13 @@
     <t>DocumentReference.extension.value[x]</t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>An explicitly assigned identifer of a variation of the content in the DocumentReference</t>
+  </si>
+  <si>
+    <t>An explicitly assigned identifer of a variation of the content in the DocumentReference.</t>
+  </si>
+  <si>
+    <t>While each resource, including the DocumentReference itself, has its own version identifier, this is a formal identifier for the logical version of the DocumentReference as a whole. It would remain constant if the resources were moved to a new server, and all got new individual resource versions, for example.</t>
   </si>
   <si>
     <t>2.0</t>
@@ -730,6 +745,12 @@
     <t>DocumentReference.extension:homeCommunityid.value[x]</t>
   </si>
   <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
     <t xml:space="preserve">type:$this}
 </t>
   </si>
@@ -1180,7 +1201,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://medcomfhir.dk/ig/xdsmetadata/ValueSet/MedCom-xds-typecode-VS"/&gt;
+  &lt;system value="urn:oid:1.2.208.184.100.1"/&gt;
   &lt;code value="HCOM"/&gt;
   &lt;display value="HomeCareObservation message"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -1297,7 +1318,7 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-organization|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitionerrole|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitioner|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person|Device) &lt;&lt;bundled&gt;&gt;
+    <t xml:space="preserve">Reference(http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-organization|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitionerrole|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitioner|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person|Device) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -1327,6 +1348,19 @@
   </si>
   <si>
     <t>The organization who authored the document.</t>
+  </si>
+  <si>
+    <t>DocumentReference.author:person</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitionerrole|http://medcomfhir.dk/ig/document/StructureDefinition/medcom-document-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+</t>
+  </si>
+  <si>
+    <t>A person/role/patient/device author of the document.</t>
   </si>
   <si>
     <t>DocumentReference.authenticator</t>
@@ -2381,7 +2415,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK180"/>
+  <dimension ref="A1:AK181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.7265625" customWidth="true" bestFit="true"/>
@@ -2403,7 +2437,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="76.671875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="43.64453125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
@@ -4658,12 +4692,14 @@
         <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
         <v>21</v>
@@ -4721,7 +4757,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>110</v>
@@ -4732,10 +4768,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4835,10 +4871,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4938,10 +4974,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4967,13 +5003,13 @@
         <v>123</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
@@ -4981,7 +5017,7 @@
       </c>
       <c r="R25" s="2"/>
       <c r="S25" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>21</v>
@@ -5023,7 +5059,7 @@
         <v>21</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>82</v>
@@ -5043,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -5054,7 +5090,7 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5072,12 +5108,14 @@
         <v>96</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
         <v>21</v>
@@ -5087,7 +5125,7 @@
         <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>21</v>
@@ -5126,7 +5164,7 @@
         <v>21</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>74</v>
@@ -5146,13 +5184,13 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>195</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>21</v>
@@ -5174,13 +5212,13 @@
         <v>21</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -5251,10 +5289,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5354,10 +5392,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5457,10 +5495,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5486,13 +5524,13 @@
         <v>123</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -5500,7 +5538,7 @@
       </c>
       <c r="R30" s="2"/>
       <c r="S30" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>21</v>
@@ -5542,7 +5580,7 @@
         <v>21</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
@@ -5562,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5591,10 +5629,10 @@
         <v>135</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -5633,17 +5671,17 @@
         <v>21</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AD31" s="2"/>
       <c r="AE31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>74</v>
@@ -5663,13 +5701,13 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E32" t="s" s="2">
         <v>21</v>
@@ -5694,10 +5732,10 @@
         <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -5728,7 +5766,7 @@
       </c>
       <c r="Z32" s="2"/>
       <c r="AA32" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AB32" t="s" s="2">
         <v>21</v>
@@ -5746,7 +5784,7 @@
         <v>21</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>74</v>
@@ -5766,10 +5804,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5869,10 +5907,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5974,10 +6012,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6003,16 +6041,16 @@
         <v>123</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q35" t="s" s="2">
         <v>21</v>
@@ -6061,7 +6099,7 @@
         <v>21</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
@@ -6081,10 +6119,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6110,13 +6148,13 @@
         <v>96</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
@@ -6166,7 +6204,7 @@
         <v>21</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>74</v>
@@ -6186,10 +6224,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6215,14 +6253,14 @@
         <v>157</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>21</v>
@@ -6271,7 +6309,7 @@
         <v>21</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>74</v>
@@ -6291,10 +6329,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6320,14 +6358,14 @@
         <v>96</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>21</v>
@@ -6376,7 +6414,7 @@
         <v>21</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
@@ -6396,10 +6434,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6422,19 +6460,19 @@
         <v>83</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>21</v>
@@ -6483,7 +6521,7 @@
         <v>21</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>74</v>
@@ -6503,10 +6541,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6586,7 +6624,7 @@
         <v>21</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>74</v>
@@ -6606,10 +6644,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6632,19 +6670,19 @@
         <v>83</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Q41" t="s" s="2">
         <v>21</v>
@@ -6693,7 +6731,7 @@
         <v>21</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
@@ -6713,10 +6751,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6816,10 +6854,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6921,10 +6959,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6950,16 +6988,16 @@
         <v>157</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>21</v>
@@ -6969,7 +7007,7 @@
         <v>21</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>21</v>
@@ -6987,10 +7025,10 @@
         <v>177</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AB44" t="s" s="2">
         <v>21</v>
@@ -7008,7 +7046,7 @@
         <v>21</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>74</v>
@@ -7028,10 +7066,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7054,19 +7092,19 @@
         <v>83</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>21</v>
@@ -7094,10 +7132,10 @@
         <v>139</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AB45" t="s" s="2">
         <v>21</v>
@@ -7115,7 +7153,7 @@
         <v>21</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>74</v>
@@ -7135,10 +7173,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7164,16 +7202,16 @@
         <v>123</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P46" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>21</v>
@@ -7186,7 +7224,7 @@
         <v>21</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="V46" t="s" s="2">
         <v>21</v>
@@ -7222,7 +7260,7 @@
         <v>21</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>74</v>
@@ -7242,10 +7280,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7271,13 +7309,13 @@
         <v>96</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7291,7 +7329,7 @@
         <v>21</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="V47" t="s" s="2">
         <v>21</v>
@@ -7327,7 +7365,7 @@
         <v>21</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>74</v>
@@ -7347,10 +7385,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7373,13 +7411,13 @@
         <v>83</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
@@ -7430,7 +7468,7 @@
         <v>21</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>74</v>
@@ -7450,10 +7488,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7476,16 +7514,16 @@
         <v>83</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -7535,7 +7573,7 @@
         <v>21</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>74</v>
@@ -7555,10 +7593,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7581,13 +7619,13 @@
         <v>83</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
@@ -7626,7 +7664,7 @@
         <v>21</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AD50" s="2"/>
       <c r="AE50" t="s" s="2">
@@ -7636,7 +7674,7 @@
         <v>108</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>74</v>
@@ -7656,13 +7694,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>21</v>
@@ -7684,13 +7722,13 @@
         <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -7741,7 +7779,7 @@
         <v>21</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>74</v>
@@ -7761,10 +7799,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7864,10 +7902,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7969,10 +8007,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7998,16 +8036,16 @@
         <v>157</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P54" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>21</v>
@@ -8017,7 +8055,7 @@
         <v>21</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>21</v>
@@ -8035,10 +8073,10 @@
         <v>177</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AB54" t="s" s="2">
         <v>21</v>
@@ -8056,7 +8094,7 @@
         <v>21</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>74</v>
@@ -8076,10 +8114,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8102,19 +8140,19 @@
         <v>83</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P55" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>21</v>
@@ -8142,10 +8180,10 @@
         <v>139</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>21</v>
@@ -8163,7 +8201,7 @@
         <v>21</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>74</v>
@@ -8183,10 +8221,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8212,29 +8250,29 @@
         <v>123</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P56" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="R56" s="2"/>
       <c r="S56" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="U56" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="V56" t="s" s="2">
         <v>21</v>
@@ -8270,7 +8308,7 @@
         <v>21</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>74</v>
@@ -8290,10 +8328,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8319,13 +8357,13 @@
         <v>96</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
@@ -8339,7 +8377,7 @@
         <v>21</v>
       </c>
       <c r="U57" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="V57" t="s" s="2">
         <v>21</v>
@@ -8375,7 +8413,7 @@
         <v>21</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>74</v>
@@ -8387,7 +8425,7 @@
         <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58">
@@ -8395,10 +8433,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8421,13 +8459,13 @@
         <v>83</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -8478,7 +8516,7 @@
         <v>21</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>74</v>
@@ -8498,10 +8536,10 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8524,16 +8562,16 @@
         <v>83</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
@@ -8583,7 +8621,7 @@
         <v>21</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>74</v>
@@ -8603,10 +8641,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8632,13 +8670,13 @@
         <v>157</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8668,7 +8706,7 @@
       </c>
       <c r="Z60" s="2"/>
       <c r="AA60" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AB60" t="s" s="2">
         <v>21</v>
@@ -8686,7 +8724,7 @@
         <v>21</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>82</v>
@@ -8706,10 +8744,10 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8735,13 +8773,13 @@
         <v>157</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8770,10 +8808,10 @@
         <v>177</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>21</v>
@@ -8791,7 +8829,7 @@
         <v>21</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>74</v>
@@ -8811,10 +8849,10 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8837,16 +8875,16 @@
         <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8875,10 +8913,10 @@
         <v>161</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>21</v>
@@ -8896,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>74</v>
@@ -8916,10 +8954,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9019,10 +9057,10 @@
         <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9124,10 +9162,10 @@
         <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9153,16 +9191,16 @@
         <v>135</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>21</v>
@@ -9172,7 +9210,7 @@
         <v>21</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>21</v>
@@ -9191,7 +9229,7 @@
       </c>
       <c r="Z65" s="2"/>
       <c r="AA65" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>21</v>
@@ -9209,7 +9247,7 @@
         <v>21</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>74</v>
@@ -9229,10 +9267,10 @@
         <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9258,16 +9296,16 @@
         <v>96</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="P66" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>21</v>
@@ -9316,7 +9354,7 @@
         <v>21</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>74</v>
@@ -9336,14 +9374,14 @@
         <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" t="s" s="2">
@@ -9362,16 +9400,16 @@
         <v>83</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9401,7 +9439,7 @@
       </c>
       <c r="Z67" s="2"/>
       <c r="AA67" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AB67" t="s" s="2">
         <v>21</v>
@@ -9419,7 +9457,7 @@
         <v>21</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>74</v>
@@ -9439,10 +9477,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9542,10 +9580,10 @@
         <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9647,10 +9685,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9676,16 +9714,16 @@
         <v>135</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="P70" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="Q70" t="s" s="2">
         <v>21</v>
@@ -9734,7 +9772,7 @@
         <v>21</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>74</v>
@@ -9754,10 +9792,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9857,10 +9895,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9962,10 +10000,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9991,16 +10029,16 @@
         <v>123</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P73" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q73" t="s" s="2">
         <v>21</v>
@@ -10049,7 +10087,7 @@
         <v>21</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>74</v>
@@ -10069,10 +10107,10 @@
         <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10098,13 +10136,13 @@
         <v>96</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -10154,7 +10192,7 @@
         <v>21</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>74</v>
@@ -10174,10 +10212,10 @@
         <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10203,14 +10241,14 @@
         <v>157</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>21</v>
@@ -10259,7 +10297,7 @@
         <v>21</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>74</v>
@@ -10279,10 +10317,10 @@
         <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10308,14 +10346,14 @@
         <v>96</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>21</v>
@@ -10364,7 +10402,7 @@
         <v>21</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>74</v>
@@ -10384,10 +10422,10 @@
         <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10410,19 +10448,19 @@
         <v>83</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P77" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>21</v>
@@ -10471,7 +10509,7 @@
         <v>21</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>74</v>
@@ -10491,10 +10529,10 @@
         <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10520,16 +10558,16 @@
         <v>96</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="P78" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>21</v>
@@ -10578,7 +10616,7 @@
         <v>21</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>74</v>
@@ -10598,10 +10636,10 @@
         <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10624,13 +10662,13 @@
         <v>83</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10681,7 +10719,7 @@
         <v>21</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>74</v>
@@ -10701,14 +10739,14 @@
         <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" t="s" s="2">
@@ -10730,13 +10768,13 @@
         <v>117</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
@@ -10786,7 +10824,7 @@
         <v>21</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>74</v>
@@ -10806,10 +10844,10 @@
         <v>3</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10820,7 +10858,7 @@
         <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>83</v>
@@ -10832,16 +10870,16 @@
         <v>83</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
@@ -10879,7 +10917,7 @@
         <v>21</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AD81" s="2"/>
       <c r="AE81" t="s" s="2">
@@ -10889,7 +10927,7 @@
         <v>108</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>74</v>
@@ -10909,13 +10947,13 @@
         <v>3</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E82" t="s" s="2">
         <v>21</v>
@@ -10937,16 +10975,16 @@
         <v>83</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
@@ -10996,7 +11034,7 @@
         <v>21</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>74</v>
@@ -11016,12 +11054,14 @@
         <v>3</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="D83" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="E83" t="s" s="2">
         <v>21</v>
       </c>
@@ -11039,19 +11079,19 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
@@ -11101,13 +11141,13 @@
         <v>21</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>21</v>
@@ -11121,10 +11161,10 @@
         <v>3</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11138,7 +11178,7 @@
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>21</v>
@@ -11147,16 +11187,16 @@
         <v>21</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>319</v>
+        <v>433</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
@@ -11206,7 +11246,7 @@
         <v>21</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>74</v>
@@ -11226,10 +11266,10 @@
         <v>3</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11240,28 +11280,28 @@
         <v>74</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>432</v>
+        <v>325</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
@@ -11311,13 +11351,13 @@
         <v>21</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>21</v>
@@ -11331,10 +11371,10 @@
         <v>3</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11345,27 +11385,29 @@
         <v>74</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>96</v>
+        <v>442</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>97</v>
+        <v>443</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>21</v>
@@ -11414,19 +11456,19 @@
         <v>21</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>99</v>
+        <v>441</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87">
@@ -11434,21 +11476,21 @@
         <v>3</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
@@ -11460,17 +11502,15 @@
         <v>21</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
         <v>21</v>
@@ -11519,19 +11559,19 @@
         <v>21</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -11539,14 +11579,14 @@
         <v>3</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>439</v>
+        <v>101</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
@@ -11559,26 +11599,24 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>102</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>440</v>
+        <v>103</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="P88" t="s" s="2">
-        <v>442</v>
-      </c>
+      <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
         <v>21</v>
       </c>
@@ -11626,7 +11664,7 @@
         <v>21</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>443</v>
+        <v>109</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>74</v>
@@ -11646,44 +11684,46 @@
         <v>3</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P89" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="Q89" t="s" s="2">
         <v>21</v>
       </c>
@@ -11707,13 +11747,13 @@
         <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AB89" t="s" s="2">
         <v>21</v>
@@ -11731,19 +11771,19 @@
         <v>21</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90">
@@ -11751,10 +11791,10 @@
         <v>3</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11777,15 +11817,17 @@
         <v>83</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>451</v>
+        <v>157</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
         <v>21</v>
@@ -11810,13 +11852,13 @@
         <v>21</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>21</v>
+        <v>459</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>21</v>
@@ -11834,7 +11876,7 @@
         <v>21</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>82</v>
@@ -11854,10 +11896,10 @@
         <v>3</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11865,7 +11907,7 @@
       </c>
       <c r="F91" s="2"/>
       <c r="G91" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -11880,20 +11922,16 @@
         <v>83</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>96</v>
+        <v>461</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
         <v>21</v>
       </c>
@@ -11941,10 +11979,10 @@
         <v>21</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
@@ -11961,10 +11999,10 @@
         <v>3</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11972,13 +12010,13 @@
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>21</v>
@@ -11987,19 +12025,19 @@
         <v>83</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>292</v>
+        <v>96</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="P92" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="Q92" t="s" s="2">
         <v>21</v>
@@ -12024,13 +12062,13 @@
         <v>21</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>21</v>
@@ -12048,13 +12086,13 @@
         <v>21</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>21</v>
@@ -12068,10 +12106,10 @@
         <v>3</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12079,31 +12117,35 @@
       </c>
       <c r="F93" s="2"/>
       <c r="G93" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>97</v>
+        <v>470</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="Q93" t="s" s="2">
         <v>21</v>
       </c>
@@ -12127,13 +12169,13 @@
         <v>21</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>21</v>
@@ -12151,19 +12193,19 @@
         <v>21</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>99</v>
+        <v>469</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94">
@@ -12171,21 +12213,21 @@
         <v>3</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>21</v>
@@ -12197,17 +12239,15 @@
         <v>21</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
         <v>21</v>
@@ -12244,31 +12284,31 @@
         <v>21</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD94" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
@@ -12276,46 +12316,44 @@
         <v>3</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P95" s="2"/>
       <c r="Q95" t="s" s="2">
         <v>21</v>
       </c>
@@ -12351,19 +12389,19 @@
         <v>21</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>74</v>
@@ -12375,7 +12413,7 @@
         <v>21</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="96">
@@ -12383,10 +12421,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12394,31 +12432,35 @@
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>97</v>
+        <v>378</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="Q96" t="s" s="2">
         <v>21</v>
       </c>
@@ -12466,19 +12508,19 @@
         <v>21</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97">
@@ -12486,21 +12528,21 @@
         <v>3</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>21</v>
@@ -12512,17 +12554,15 @@
         <v>21</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
         <v>21</v>
@@ -12559,31 +12599,31 @@
         <v>21</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
@@ -12591,46 +12631,44 @@
         <v>3</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
         <v>21</v>
       </c>
@@ -12666,31 +12704,31 @@
         <v>21</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD98" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99">
@@ -12698,10 +12736,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12709,13 +12747,13 @@
       </c>
       <c r="F99" s="2"/>
       <c r="G99" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>21</v>
@@ -12724,18 +12762,20 @@
         <v>83</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M99" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="O99" t="s" s="2">
+      <c r="P99" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="P99" s="2"/>
       <c r="Q99" t="s" s="2">
         <v>21</v>
       </c>
@@ -12803,10 +12843,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12814,13 +12854,13 @@
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>21</v>
@@ -12829,7 +12869,7 @@
         <v>83</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>254</v>
@@ -12837,10 +12877,10 @@
       <c r="N100" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
         <v>21</v>
       </c>
@@ -12908,10 +12948,10 @@
         <v>3</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12919,13 +12959,13 @@
       </c>
       <c r="F101" s="2"/>
       <c r="G101" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>21</v>
@@ -12934,7 +12974,7 @@
         <v>83</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>260</v>
@@ -13013,10 +13053,10 @@
         <v>3</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13039,19 +13079,17 @@
         <v>83</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="Q102" t="s" s="2">
         <v>21</v>
@@ -13100,7 +13138,7 @@
         <v>21</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>74</v>
@@ -13120,10 +13158,10 @@
         <v>3</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13146,19 +13184,19 @@
         <v>83</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>96</v>
+        <v>272</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="P103" t="s" s="2">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="Q103" t="s" s="2">
         <v>21</v>
@@ -13207,7 +13245,7 @@
         <v>21</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>74</v>
@@ -13227,10 +13265,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13238,13 +13276,13 @@
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
         <v>21</v>
@@ -13253,16 +13291,20 @@
         <v>83</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>476</v>
+        <v>386</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="Q104" t="s" s="2">
         <v>21</v>
       </c>
@@ -13310,13 +13352,13 @@
         <v>21</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>475</v>
+        <v>390</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>21</v>
@@ -13330,10 +13372,10 @@
         <v>3</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13341,28 +13383,28 @@
       </c>
       <c r="F105" s="2"/>
       <c r="G105" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>96</v>
+        <v>442</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>97</v>
+        <v>486</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>98</v>
+        <v>487</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -13413,19 +13455,19 @@
         <v>21</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>99</v>
+        <v>485</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="106">
@@ -13433,21 +13475,21 @@
         <v>3</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>21</v>
@@ -13459,17 +13501,15 @@
         <v>21</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
         <v>21</v>
@@ -13518,19 +13558,19 @@
         <v>21</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
@@ -13538,14 +13578,14 @@
         <v>3</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
-        <v>439</v>
+        <v>101</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
@@ -13558,26 +13598,24 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>102</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>440</v>
+        <v>103</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="P107" t="s" s="2">
-        <v>442</v>
-      </c>
+      <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
         <v>21</v>
       </c>
@@ -13625,7 +13663,7 @@
         <v>21</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>443</v>
+        <v>109</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>74</v>
@@ -13645,42 +13683,46 @@
         <v>3</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>482</v>
+        <v>102</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O108" s="2"/>
-      <c r="P108" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="Q108" t="s" s="2">
         <v>21</v>
       </c>
@@ -13728,19 +13770,19 @@
         <v>21</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109">
@@ -13748,10 +13790,10 @@
         <v>3</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13759,28 +13801,28 @@
       </c>
       <c r="F109" s="2"/>
       <c r="G109" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>96</v>
+        <v>492</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -13831,10 +13873,10 @@
         <v>21</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>99</v>
+        <v>491</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
@@ -13843,7 +13885,7 @@
         <v>21</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="110">
@@ -13851,21 +13893,21 @@
         <v>3</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
@@ -13877,17 +13919,15 @@
         <v>21</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>21</v>
@@ -13924,31 +13964,31 @@
         <v>21</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD110" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111">
@@ -13956,44 +13996,44 @@
         <v>3</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
         <v>21</v>
       </c>
@@ -14005,7 +14045,7 @@
         <v>21</v>
       </c>
       <c r="U111" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="V111" t="s" s="2">
         <v>21</v>
@@ -14017,41 +14057,43 @@
         <v>21</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z111" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AA111" t="s" s="2">
-        <v>492</v>
+        <v>21</v>
       </c>
       <c r="AB111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD111" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>493</v>
+        <v>109</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
@@ -14059,10 +14101,10 @@
         <v>3</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14088,14 +14130,14 @@
         <v>157</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>21</v>
@@ -14108,7 +14150,7 @@
         <v>21</v>
       </c>
       <c r="U112" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="V112" t="s" s="2">
         <v>21</v>
@@ -14120,11 +14162,11 @@
         <v>21</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="Z112" s="2"/>
       <c r="AA112" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AB112" t="s" s="2">
         <v>21</v>
@@ -14142,7 +14184,7 @@
         <v>21</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>74</v>
@@ -14162,10 +14204,10 @@
         <v>3</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14173,34 +14215,32 @@
       </c>
       <c r="F113" s="2"/>
       <c r="G113" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>502</v>
+        <v>157</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q113" t="s" s="2">
         <v>21</v>
@@ -14213,7 +14253,7 @@
         <v>21</v>
       </c>
       <c r="U113" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="V113" t="s" s="2">
         <v>21</v>
@@ -14225,13 +14265,11 @@
         <v>21</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Z113" s="2"/>
       <c r="AA113" t="s" s="2">
-        <v>21</v>
+        <v>509</v>
       </c>
       <c r="AB113" t="s" s="2">
         <v>21</v>
@@ -14249,7 +14287,7 @@
         <v>21</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>74</v>
@@ -14269,10 +14307,10 @@
         <v>3</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14280,34 +14318,34 @@
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="P114" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Q114" t="s" s="2">
         <v>21</v>
@@ -14320,7 +14358,7 @@
         <v>21</v>
       </c>
       <c r="U114" t="s" s="2">
-        <v>514</v>
+        <v>21</v>
       </c>
       <c r="V114" t="s" s="2">
         <v>21</v>
@@ -14356,7 +14394,7 @@
         <v>21</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>74</v>
@@ -14376,10 +14414,10 @@
         <v>3</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -14387,7 +14425,7 @@
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -14402,19 +14440,19 @@
         <v>83</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P115" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Q115" t="s" s="2">
         <v>21</v>
@@ -14427,7 +14465,7 @@
         <v>21</v>
       </c>
       <c r="U115" t="s" s="2">
-        <v>21</v>
+        <v>524</v>
       </c>
       <c r="V115" t="s" s="2">
         <v>21</v>
@@ -14463,7 +14501,7 @@
         <v>21</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>74</v>
@@ -14483,10 +14521,10 @@
         <v>3</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14509,19 +14547,19 @@
         <v>83</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="P116" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>21</v>
@@ -14570,7 +14608,7 @@
         <v>21</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>74</v>
@@ -14590,10 +14628,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14601,7 +14639,7 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>82</v>
@@ -14616,17 +14654,19 @@
         <v>83</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>96</v>
+        <v>512</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P117" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="Q117" t="s" s="2">
         <v>21</v>
@@ -14639,7 +14679,7 @@
         <v>21</v>
       </c>
       <c r="U117" t="s" s="2">
-        <v>533</v>
+        <v>21</v>
       </c>
       <c r="V117" t="s" s="2">
         <v>21</v>
@@ -14675,7 +14715,7 @@
         <v>21</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>74</v>
@@ -14695,10 +14735,10 @@
         <v>3</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -14721,17 +14761,17 @@
         <v>83</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>536</v>
+        <v>96</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="Q118" t="s" s="2">
         <v>21</v>
@@ -14744,7 +14784,7 @@
         <v>21</v>
       </c>
       <c r="U118" t="s" s="2">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="V118" t="s" s="2">
         <v>21</v>
@@ -14780,7 +14820,7 @@
         <v>21</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>74</v>
@@ -14792,7 +14832,7 @@
         <v>21</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>541</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119">
@@ -14800,10 +14840,10 @@
         <v>3</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -14826,18 +14866,18 @@
         <v>83</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>135</v>
+        <v>546</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="P119" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="Q119" t="s" s="2">
         <v>21</v>
       </c>
@@ -14861,11 +14901,13 @@
         <v>21</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z119" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AA119" t="s" s="2">
-        <v>546</v>
+        <v>21</v>
       </c>
       <c r="AB119" t="s" s="2">
         <v>21</v>
@@ -14883,7 +14925,7 @@
         <v>21</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>74</v>
@@ -14895,7 +14937,7 @@
         <v>21</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>94</v>
+        <v>551</v>
       </c>
     </row>
     <row r="120">
@@ -14903,10 +14945,10 @@
         <v>3</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -14914,30 +14956,32 @@
       </c>
       <c r="F120" s="2"/>
       <c r="G120" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>97</v>
+        <v>553</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
         <v>21</v>
@@ -14962,13 +15006,11 @@
         <v>21</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Z120" s="2"/>
       <c r="AA120" t="s" s="2">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="AB120" t="s" s="2">
         <v>21</v>
@@ -14986,7 +15028,7 @@
         <v>21</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>99</v>
+        <v>552</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>74</v>
@@ -14998,7 +15040,7 @@
         <v>21</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="121">
@@ -15006,21 +15048,21 @@
         <v>3</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>21</v>
@@ -15032,17 +15074,15 @@
         <v>21</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
         <v>21</v>
@@ -15079,31 +15119,31 @@
         <v>21</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD121" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -15111,46 +15151,44 @@
         <v>3</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
         <v>21</v>
       </c>
@@ -15186,31 +15224,31 @@
         <v>21</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD122" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123">
@@ -15218,10 +15256,10 @@
         <v>3</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15229,13 +15267,13 @@
       </c>
       <c r="F123" s="2"/>
       <c r="G123" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>21</v>
@@ -15244,18 +15282,20 @@
         <v>83</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M123" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="O123" t="s" s="2">
+      <c r="P123" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
         <v>21</v>
       </c>
@@ -15323,10 +15363,10 @@
         <v>3</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15334,13 +15374,13 @@
       </c>
       <c r="F124" s="2"/>
       <c r="G124" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>21</v>
@@ -15349,7 +15389,7 @@
         <v>83</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="M124" t="s" s="2">
         <v>254</v>
@@ -15357,10 +15397,10 @@
       <c r="N124" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
         <v>21</v>
       </c>
@@ -15428,10 +15468,10 @@
         <v>3</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15454,7 +15494,7 @@
         <v>83</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>260</v>
@@ -15533,10 +15573,10 @@
         <v>3</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15544,13 +15584,13 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>21</v>
@@ -15559,19 +15599,17 @@
         <v>83</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="Q126" t="s" s="2">
         <v>21</v>
@@ -15620,7 +15658,7 @@
         <v>21</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>74</v>
@@ -15640,10 +15678,10 @@
         <v>3</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -15651,13 +15689,13 @@
       </c>
       <c r="F127" s="2"/>
       <c r="G127" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J127" t="s" s="2">
         <v>21</v>
@@ -15666,18 +15704,20 @@
         <v>83</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>432</v>
+        <v>272</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>555</v>
+        <v>273</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>556</v>
+        <v>274</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="P127" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="Q127" t="s" s="2">
         <v>21</v>
       </c>
@@ -15725,7 +15765,7 @@
         <v>21</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>554</v>
+        <v>277</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>74</v>
@@ -15745,10 +15785,10 @@
         <v>3</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -15756,30 +15796,32 @@
       </c>
       <c r="F128" s="2"/>
       <c r="G128" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>96</v>
+        <v>442</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>97</v>
+        <v>565</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P128" s="2"/>
       <c r="Q128" t="s" s="2">
         <v>21</v>
@@ -15828,7 +15870,7 @@
         <v>21</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>99</v>
+        <v>564</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>74</v>
@@ -15840,7 +15882,7 @@
         <v>21</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="129">
@@ -15848,21 +15890,21 @@
         <v>3</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>21</v>
@@ -15874,17 +15916,15 @@
         <v>21</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O129" s="2"/>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
         <v>21</v>
@@ -15933,19 +15973,19 @@
         <v>21</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130">
@@ -15953,14 +15993,14 @@
         <v>3</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
-        <v>439</v>
+        <v>101</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" t="s" s="2">
@@ -15973,26 +16013,24 @@
         <v>21</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L130" t="s" s="2">
         <v>102</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>440</v>
+        <v>103</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="P130" t="s" s="2">
-        <v>442</v>
-      </c>
+      <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
         <v>21</v>
       </c>
@@ -16040,7 +16078,7 @@
         <v>21</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>443</v>
+        <v>109</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>74</v>
@@ -16060,14 +16098,14 @@
         <v>3</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s" s="2">
@@ -16080,22 +16118,26 @@
         <v>21</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>562</v>
+        <v>102</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>563</v>
+        <v>450</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="Q131" t="s" s="2">
         <v>21</v>
       </c>
@@ -16143,7 +16185,7 @@
         <v>21</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>561</v>
+        <v>453</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>74</v>
@@ -16155,7 +16197,7 @@
         <v>21</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132">
@@ -16163,10 +16205,10 @@
         <v>3</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16180,7 +16222,7 @@
         <v>75</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J132" t="s" s="2">
         <v>21</v>
@@ -16189,17 +16231,15 @@
         <v>21</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>292</v>
+        <v>572</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
         <v>21</v>
@@ -16224,11 +16264,13 @@
         <v>21</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Z132" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AA132" t="s" s="2">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="AB132" t="s" s="2">
         <v>21</v>
@@ -16246,7 +16288,7 @@
         <v>21</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>74</v>
@@ -16266,10 +16308,10 @@
         <v>3</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16280,10 +16322,10 @@
         <v>74</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>21</v>
@@ -16292,15 +16334,17 @@
         <v>21</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>97</v>
+        <v>576</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
         <v>21</v>
@@ -16325,13 +16369,11 @@
         <v>21</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Z133" s="2"/>
       <c r="AA133" t="s" s="2">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="AB133" t="s" s="2">
         <v>21</v>
@@ -16349,19 +16391,19 @@
         <v>21</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>99</v>
+        <v>575</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134">
@@ -16369,21 +16411,21 @@
         <v>3</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>21</v>
@@ -16395,17 +16437,15 @@
         <v>21</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
         <v>21</v>
@@ -16442,31 +16482,31 @@
         <v>21</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD134" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135">
@@ -16474,14 +16514,14 @@
         <v>3</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
@@ -16497,23 +16537,21 @@
         <v>21</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P135" s="2"/>
       <c r="Q135" t="s" s="2">
         <v>21</v>
       </c>
@@ -16549,19 +16587,19 @@
         <v>21</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD135" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>74</v>
@@ -16573,7 +16611,7 @@
         <v>21</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136">
@@ -16581,10 +16619,10 @@
         <v>3</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -16595,7 +16633,7 @@
         <v>74</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>21</v>
@@ -16604,19 +16642,23 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>97</v>
+        <v>378</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="Q136" t="s" s="2">
         <v>21</v>
       </c>
@@ -16664,19 +16706,19 @@
         <v>21</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="137">
@@ -16684,21 +16726,21 @@
         <v>3</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>21</v>
@@ -16710,17 +16752,15 @@
         <v>21</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
         <v>21</v>
@@ -16757,31 +16797,31 @@
         <v>21</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD137" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138">
@@ -16789,46 +16829,44 @@
         <v>3</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="P138" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P138" s="2"/>
       <c r="Q138" t="s" s="2">
         <v>21</v>
       </c>
@@ -16864,31 +16902,31 @@
         <v>21</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD138" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139">
@@ -16896,10 +16934,10 @@
         <v>3</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -16907,13 +16945,13 @@
       </c>
       <c r="F139" s="2"/>
       <c r="G139" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J139" t="s" s="2">
         <v>21</v>
@@ -16922,18 +16960,20 @@
         <v>83</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M139" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="O139" t="s" s="2">
+      <c r="P139" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
         <v>21</v>
       </c>
@@ -17001,10 +17041,10 @@
         <v>3</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -17012,13 +17052,13 @@
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>21</v>
@@ -17027,7 +17067,7 @@
         <v>83</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="M140" t="s" s="2">
         <v>254</v>
@@ -17035,10 +17075,10 @@
       <c r="N140" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="P140" s="2"/>
       <c r="Q140" t="s" s="2">
         <v>21</v>
       </c>
@@ -17106,10 +17146,10 @@
         <v>3</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -17117,13 +17157,13 @@
       </c>
       <c r="F141" s="2"/>
       <c r="G141" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J141" t="s" s="2">
         <v>21</v>
@@ -17132,7 +17172,7 @@
         <v>83</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="M141" t="s" s="2">
         <v>260</v>
@@ -17211,10 +17251,10 @@
         <v>3</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -17237,19 +17277,17 @@
         <v>83</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="Q142" t="s" s="2">
         <v>21</v>
@@ -17298,7 +17336,7 @@
         <v>21</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>74</v>
@@ -17318,10 +17356,10 @@
         <v>3</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -17344,19 +17382,19 @@
         <v>83</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>96</v>
+        <v>272</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="P143" t="s" s="2">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="Q143" t="s" s="2">
         <v>21</v>
@@ -17405,7 +17443,7 @@
         <v>21</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>74</v>
@@ -17425,10 +17463,10 @@
         <v>3</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -17436,13 +17474,13 @@
       </c>
       <c r="F144" s="2"/>
       <c r="G144" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J144" t="s" s="2">
         <v>21</v>
@@ -17451,16 +17489,20 @@
         <v>83</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>314</v>
+        <v>96</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>582</v>
+        <v>386</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O144" s="2"/>
-      <c r="P144" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="Q144" t="s" s="2">
         <v>21</v>
       </c>
@@ -17508,7 +17550,7 @@
         <v>21</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>581</v>
+        <v>390</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>74</v>
@@ -17528,10 +17570,10 @@
         <v>3</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -17539,28 +17581,28 @@
       </c>
       <c r="F145" s="2"/>
       <c r="G145" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>96</v>
+        <v>320</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>97</v>
+        <v>592</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>98</v>
+        <v>593</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -17611,7 +17653,7 @@
         <v>21</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>99</v>
+        <v>591</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>74</v>
@@ -17623,7 +17665,7 @@
         <v>21</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146">
@@ -17631,21 +17673,21 @@
         <v>3</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>21</v>
@@ -17657,17 +17699,15 @@
         <v>21</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" s="2"/>
       <c r="Q146" t="s" s="2">
         <v>21</v>
@@ -17704,31 +17744,31 @@
         <v>21</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD146" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
@@ -17736,42 +17776,42 @@
         <v>3</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>536</v>
+        <v>102</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>587</v>
+        <v>103</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>588</v>
+        <v>104</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>589</v>
+        <v>105</v>
       </c>
       <c r="P147" s="2"/>
       <c r="Q147" t="s" s="2">
@@ -17809,31 +17849,31 @@
         <v>21</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD147" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>590</v>
+        <v>109</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>591</v>
+        <v>21</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="148">
@@ -17841,10 +17881,10 @@
         <v>3</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -17852,7 +17892,7 @@
       </c>
       <c r="F148" s="2"/>
       <c r="G148" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -17867,24 +17907,22 @@
         <v>83</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="P148" s="2"/>
       <c r="Q148" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="R148" t="s" s="2">
-        <v>596</v>
-      </c>
+      <c r="R148" s="2"/>
       <c r="S148" t="s" s="2">
         <v>21</v>
       </c>
@@ -17928,7 +17966,7 @@
         <v>21</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>74</v>
@@ -17937,7 +17975,7 @@
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>94</v>
@@ -17948,10 +17986,10 @@
         <v>3</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -17959,7 +17997,7 @@
       </c>
       <c r="F149" s="2"/>
       <c r="G149" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>82</v>
@@ -17971,23 +18009,27 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>292</v>
+        <v>546</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O149" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="P149" s="2"/>
       <c r="Q149" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="R149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="S149" t="s" s="2">
         <v>21</v>
       </c>
@@ -18007,38 +18049,40 @@
         <v>21</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z149" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AA149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>94</v>
@@ -18049,10 +18093,10 @@
         <v>3</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -18060,13 +18104,13 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J150" t="s" s="2">
         <v>21</v>
@@ -18075,13 +18119,13 @@
         <v>21</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>97</v>
+        <v>609</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>98</v>
+        <v>610</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -18108,13 +18152,11 @@
         <v>21</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Z150" s="2"/>
       <c r="AA150" t="s" s="2">
-        <v>21</v>
+        <v>611</v>
       </c>
       <c r="AB150" t="s" s="2">
         <v>21</v>
@@ -18132,7 +18174,7 @@
         <v>21</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>99</v>
+        <v>608</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>74</v>
@@ -18144,7 +18186,7 @@
         <v>21</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151">
@@ -18152,21 +18194,21 @@
         <v>3</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
@@ -18178,17 +18220,15 @@
         <v>21</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" s="2"/>
       <c r="Q151" t="s" s="2">
         <v>21</v>
@@ -18225,31 +18265,31 @@
         <v>21</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD151" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
@@ -18257,46 +18297,44 @@
         <v>3</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P152" s="2"/>
       <c r="Q152" t="s" s="2">
         <v>21</v>
       </c>
@@ -18332,19 +18370,19 @@
         <v>21</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD152" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>74</v>
@@ -18356,7 +18394,7 @@
         <v>21</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="153">
@@ -18364,10 +18402,10 @@
         <v>3</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -18375,31 +18413,35 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>97</v>
+        <v>378</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P153" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="Q153" t="s" s="2">
         <v>21</v>
       </c>
@@ -18447,19 +18489,19 @@
         <v>21</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="154">
@@ -18467,21 +18509,21 @@
         <v>3</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>21</v>
@@ -18493,17 +18535,15 @@
         <v>21</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" s="2"/>
       <c r="Q154" t="s" s="2">
         <v>21</v>
@@ -18540,31 +18580,31 @@
         <v>21</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD154" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
@@ -18572,46 +18612,44 @@
         <v>3</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
         <v>21</v>
       </c>
@@ -18647,31 +18685,31 @@
         <v>21</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD155" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="156">
@@ -18679,10 +18717,10 @@
         <v>3</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -18690,13 +18728,13 @@
       </c>
       <c r="F156" s="2"/>
       <c r="G156" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I156" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J156" t="s" s="2">
         <v>21</v>
@@ -18705,18 +18743,20 @@
         <v>83</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M156" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="O156" t="s" s="2">
+      <c r="P156" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
         <v>21</v>
       </c>
@@ -18784,10 +18824,10 @@
         <v>3</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -18795,13 +18835,13 @@
       </c>
       <c r="F157" s="2"/>
       <c r="G157" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J157" t="s" s="2">
         <v>21</v>
@@ -18810,7 +18850,7 @@
         <v>83</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="M157" t="s" s="2">
         <v>254</v>
@@ -18818,10 +18858,10 @@
       <c r="N157" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="P157" s="2"/>
       <c r="Q157" t="s" s="2">
         <v>21</v>
       </c>
@@ -18889,10 +18929,10 @@
         <v>3</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -18915,7 +18955,7 @@
         <v>83</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>260</v>
@@ -18994,10 +19034,10 @@
         <v>3</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -19005,13 +19045,13 @@
       </c>
       <c r="F159" s="2"/>
       <c r="G159" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J159" t="s" s="2">
         <v>21</v>
@@ -19020,19 +19060,17 @@
         <v>83</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P159" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>21</v>
@@ -19081,7 +19119,7 @@
         <v>21</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>74</v>
@@ -19101,10 +19139,10 @@
         <v>3</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -19127,19 +19165,19 @@
         <v>83</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>96</v>
+        <v>272</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="P160" t="s" s="2">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="Q160" t="s" s="2">
         <v>21</v>
@@ -19188,7 +19226,7 @@
         <v>21</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>74</v>
@@ -19208,10 +19246,10 @@
         <v>3</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -19219,34 +19257,34 @@
       </c>
       <c r="F161" s="2"/>
       <c r="G161" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K161" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="J161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="L161" t="s" s="2">
-        <v>292</v>
+        <v>96</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>614</v>
+        <v>386</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>615</v>
+        <v>387</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>616</v>
+        <v>388</v>
       </c>
       <c r="P161" t="s" s="2">
-        <v>617</v>
+        <v>389</v>
       </c>
       <c r="Q161" t="s" s="2">
         <v>21</v>
@@ -19271,11 +19309,13 @@
         <v>21</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z161" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AA161" t="s" s="2">
-        <v>618</v>
+        <v>21</v>
       </c>
       <c r="AB161" t="s" s="2">
         <v>21</v>
@@ -19293,7 +19333,7 @@
         <v>21</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>613</v>
+        <v>390</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>74</v>
@@ -19313,10 +19353,10 @@
         <v>3</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -19324,13 +19364,13 @@
       </c>
       <c r="F162" s="2"/>
       <c r="G162" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J162" t="s" s="2">
         <v>21</v>
@@ -19339,16 +19379,20 @@
         <v>21</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>97</v>
+        <v>624</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O162" s="2"/>
-      <c r="P162" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P162" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="Q162" t="s" s="2">
         <v>21</v>
       </c>
@@ -19372,13 +19416,11 @@
         <v>21</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Z162" s="2"/>
       <c r="AA162" t="s" s="2">
-        <v>21</v>
+        <v>628</v>
       </c>
       <c r="AB162" t="s" s="2">
         <v>21</v>
@@ -19396,7 +19438,7 @@
         <v>21</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>99</v>
+        <v>623</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>74</v>
@@ -19408,7 +19450,7 @@
         <v>21</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="163">
@@ -19416,21 +19458,21 @@
         <v>3</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>21</v>
@@ -19442,17 +19484,15 @@
         <v>21</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O163" s="2"/>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
         <v>21</v>
@@ -19489,31 +19529,31 @@
         <v>21</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD163" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164">
@@ -19521,46 +19561,44 @@
         <v>3</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F164" s="2"/>
       <c r="G164" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I164" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
         <v>21</v>
       </c>
@@ -19596,19 +19634,19 @@
         <v>21</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD164" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>74</v>
@@ -19620,7 +19658,7 @@
         <v>21</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165">
@@ -19628,10 +19666,10 @@
         <v>3</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -19639,31 +19677,35 @@
       </c>
       <c r="F165" s="2"/>
       <c r="G165" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I165" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>97</v>
+        <v>378</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O165" s="2"/>
-      <c r="P165" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P165" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="Q165" t="s" s="2">
         <v>21</v>
       </c>
@@ -19711,19 +19753,19 @@
         <v>21</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="166">
@@ -19731,21 +19773,21 @@
         <v>3</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>21</v>
@@ -19757,17 +19799,15 @@
         <v>21</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
         <v>21</v>
@@ -19804,31 +19844,31 @@
         <v>21</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD166" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
@@ -19836,46 +19876,44 @@
         <v>3</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="P167" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
         <v>21</v>
       </c>
@@ -19911,31 +19949,31 @@
         <v>21</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD167" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="168">
@@ -19943,10 +19981,10 @@
         <v>3</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -19954,13 +19992,13 @@
       </c>
       <c r="F168" s="2"/>
       <c r="G168" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J168" t="s" s="2">
         <v>21</v>
@@ -19969,18 +20007,20 @@
         <v>83</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="O168" t="s" s="2">
+      <c r="P168" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
         <v>21</v>
       </c>
@@ -20048,10 +20088,10 @@
         <v>3</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -20059,13 +20099,13 @@
       </c>
       <c r="F169" s="2"/>
       <c r="G169" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J169" t="s" s="2">
         <v>21</v>
@@ -20074,7 +20114,7 @@
         <v>83</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>254</v>
@@ -20082,10 +20122,10 @@
       <c r="N169" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="O169" s="2"/>
-      <c r="P169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
         <v>21</v>
       </c>
@@ -20153,10 +20193,10 @@
         <v>3</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -20179,7 +20219,7 @@
         <v>83</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="M170" t="s" s="2">
         <v>260</v>
@@ -20258,10 +20298,10 @@
         <v>3</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -20269,13 +20309,13 @@
       </c>
       <c r="F171" s="2"/>
       <c r="G171" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I171" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J171" t="s" s="2">
         <v>21</v>
@@ -20284,19 +20324,17 @@
         <v>83</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N171" t="s" s="2">
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P171" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="Q171" t="s" s="2">
         <v>21</v>
@@ -20345,7 +20383,7 @@
         <v>21</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>74</v>
@@ -20365,10 +20403,10 @@
         <v>3</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -20391,19 +20429,19 @@
         <v>83</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>96</v>
+        <v>272</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="P172" t="s" s="2">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="Q172" t="s" s="2">
         <v>21</v>
@@ -20452,7 +20490,7 @@
         <v>21</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>74</v>
@@ -20472,10 +20510,10 @@
         <v>3</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -20483,31 +20521,35 @@
       </c>
       <c r="F173" s="2"/>
       <c r="G173" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K173" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="J173" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K173" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="L173" t="s" s="2">
-        <v>631</v>
+        <v>96</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>632</v>
+        <v>386</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O173" s="2"/>
-      <c r="P173" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="Q173" t="s" s="2">
         <v>21</v>
       </c>
@@ -20555,7 +20597,7 @@
         <v>21</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>630</v>
+        <v>390</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>74</v>
@@ -20575,10 +20617,10 @@
         <v>3</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -20586,13 +20628,13 @@
       </c>
       <c r="F174" s="2"/>
       <c r="G174" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I174" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J174" t="s" s="2">
         <v>21</v>
@@ -20601,13 +20643,13 @@
         <v>21</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>96</v>
+        <v>641</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>97</v>
+        <v>642</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>98</v>
+        <v>643</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -20658,7 +20700,7 @@
         <v>21</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>99</v>
+        <v>640</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>74</v>
@@ -20670,7 +20712,7 @@
         <v>21</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="175">
@@ -20678,21 +20720,21 @@
         <v>3</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>21</v>
@@ -20704,17 +20746,15 @@
         <v>21</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="O175" s="2"/>
       <c r="P175" s="2"/>
       <c r="Q175" t="s" s="2">
         <v>21</v>
@@ -20751,31 +20791,31 @@
         <v>21</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="AD175" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AE175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176">
@@ -20783,42 +20823,42 @@
         <v>3</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>637</v>
+        <v>103</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>638</v>
+        <v>104</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>639</v>
+        <v>105</v>
       </c>
       <c r="P176" s="2"/>
       <c r="Q176" t="s" s="2">
@@ -20856,31 +20896,31 @@
         <v>21</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AD176" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>640</v>
+        <v>109</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>641</v>
+        <v>21</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="177">
@@ -20888,10 +20928,10 @@
         <v>3</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -20899,13 +20939,13 @@
       </c>
       <c r="F177" s="2"/>
       <c r="G177" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J177" t="s" s="2">
         <v>21</v>
@@ -20914,16 +20954,16 @@
         <v>83</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
@@ -20949,13 +20989,13 @@
         <v>21</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>646</v>
+        <v>21</v>
       </c>
       <c r="AA177" t="s" s="2">
-        <v>647</v>
+        <v>21</v>
       </c>
       <c r="AB177" t="s" s="2">
         <v>21</v>
@@ -20973,7 +21013,7 @@
         <v>21</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>74</v>
@@ -20982,7 +21022,7 @@
         <v>82</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>21</v>
+        <v>651</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>94</v>
@@ -20993,10 +21033,10 @@
         <v>3</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -21004,13 +21044,13 @@
       </c>
       <c r="F178" s="2"/>
       <c r="G178" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I178" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J178" t="s" s="2">
         <v>21</v>
@@ -21019,16 +21059,16 @@
         <v>83</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>325</v>
+        <v>123</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" t="s" s="2">
@@ -21054,13 +21094,13 @@
         <v>21</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>21</v>
+        <v>656</v>
       </c>
       <c r="AA178" t="s" s="2">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="AB178" t="s" s="2">
         <v>21</v>
@@ -21078,7 +21118,7 @@
         <v>21</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>74</v>
@@ -21098,10 +21138,10 @@
         <v>3</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -21109,13 +21149,13 @@
       </c>
       <c r="F179" s="2"/>
       <c r="G179" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I179" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J179" t="s" s="2">
         <v>21</v>
@@ -21124,16 +21164,16 @@
         <v>83</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>96</v>
+        <v>331</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="P179" s="2"/>
       <c r="Q179" t="s" s="2">
@@ -21183,7 +21223,7 @@
         <v>21</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>74</v>
@@ -21203,10 +21243,10 @@
         <v>3</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -21217,28 +21257,28 @@
         <v>74</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I180" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K180" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="J180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="L180" t="s" s="2">
-        <v>660</v>
+        <v>96</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="P180" s="2"/>
       <c r="Q180" t="s" s="2">
@@ -21288,18 +21328,123 @@
         <v>21</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="D181" s="2"/>
+      <c r="E181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F181" s="2"/>
+      <c r="G181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H181" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AJ180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK180" t="s" s="2">
+      <c r="I181" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="P181" s="2"/>
+      <c r="Q181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="R181" s="2"/>
+      <c r="S181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK181" t="s" s="2">
         <v>94</v>
       </c>
     </row>
